--- a/apps/api/assets/vocabulary/初中/人教版/人教版初中英语八年级下册.xlsx
+++ b/apps/api/assets/vocabulary/初中/人教版/人教版初中英语八年级下册.xlsx
@@ -440,7 +440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D541"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -500,6 +500,16 @@
           <t>What's the matter?</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>怎么回事?怎么啦?</t>
@@ -536,6 +546,16 @@
           <t>have a cold</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 伤风
@@ -569,6 +589,16 @@
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>have a stomachache</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -849,6 +879,16 @@
           <t>take one's temperature</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 量体温
@@ -882,6 +922,16 @@
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>have a fever</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -922,6 +972,16 @@
           <t>take breaks</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -932,6 +992,16 @@
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>take a break</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1019,6 +1089,16 @@
           <t>get off</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 下车；脱下(衣服等)；脱(衣)；下(马)
@@ -1030,6 +1110,16 @@
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>to one's surprise</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1115,6 +1205,16 @@
           <t>right away</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 立刻
@@ -1126,6 +1226,16 @@
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>get into</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1369,6 +1479,16 @@
           <t>be used to</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 惯于
@@ -1406,6 +1526,16 @@
           <t>take risks</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 冒险
@@ -1417,6 +1547,16 @@
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>take a risk</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -1569,6 +1709,16 @@
           <t>run out of</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 用光…
@@ -1604,6 +1754,16 @@
       <c r="A57" s="2" t="inlineStr">
         <is>
           <t>cut off</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -1669,6 +1829,16 @@
           <t>get out of</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 逐渐放弃(恶习)；避免；由…出来；拔出
@@ -1749,6 +1919,16 @@
           <t>be in control of</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
           <t>vt.控制,管理</t>
@@ -1805,6 +1985,16 @@
       <c r="A67" s="2" t="inlineStr">
         <is>
           <t>give up</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -1867,6 +2057,16 @@
           <t>Nancy</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
           <t>adj. 女性化的；同性恋的
@@ -1880,6 +2080,16 @@
           <t>Mandy</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
           <t>n. 曼蒂（女子名）；镇静片（等于Mandrax）</t>
@@ -1890,6 +2100,16 @@
       <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Aron Ralston</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -1973,6 +2193,16 @@
           <t>cheer up</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 鼓舞；振作一点
@@ -1984,6 +2214,16 @@
       <c r="A77" s="2" t="inlineStr">
         <is>
           <t>give out</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -2024,6 +2264,16 @@
           <t>come up with</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 想出(一个主意或计划)；提出；提供；筹措
@@ -2035,6 +2285,16 @@
       <c r="A80" s="2" t="inlineStr">
         <is>
           <t>put off</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -2098,6 +2358,16 @@
           <t>hand out</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 分；拿出来；施舍
@@ -2134,6 +2404,16 @@
           <t>used to</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">modalv. （用于过去持续或经常发生的事）曾经
@@ -2169,6 +2449,16 @@
       <c r="A87" s="2" t="inlineStr">
         <is>
           <t>care for</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -2323,6 +2613,16 @@
           <t>try out</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. (采用前)严密试验；筛矿；量(金属的)纯度
@@ -2480,6 +2780,16 @@
           <t>fix up</t>
         </is>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 〈美口〉修理；解决；组织；安顿住处
@@ -2514,6 +2824,16 @@
       <c r="A103" s="2" t="inlineStr">
         <is>
           <t>take after</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -2601,6 +2921,16 @@
           <t>Miss</t>
         </is>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
           <t>n. 女士，小姐，年轻未婚女子
@@ -2658,6 +2988,16 @@
       <c r="A110" s="2" t="inlineStr">
         <is>
           <t>make a difference</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -3070,6 +3410,16 @@
           <t>Mario</t>
         </is>
       </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
           <t>n. 马里奥（男子名）</t>
@@ -3082,6 +3432,16 @@
           <t>Jimmy</t>
         </is>
       </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
           <t>vt. 撬开
@@ -3116,6 +3476,16 @@
       <c r="A131" s="2" t="inlineStr">
         <is>
           <t>take out the rubbish</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -3248,6 +3618,16 @@
       <c r="A137" s="2" t="inlineStr">
         <is>
           <t>all the time</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -3310,6 +3690,16 @@
           <t>as soon as</t>
         </is>
       </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 一…就；见 soon 条
@@ -3564,6 +3954,16 @@
           <t>in order to</t>
         </is>
       </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 为了；从而；以便
@@ -3642,6 +4042,16 @@
       <c r="A155" s="2" t="inlineStr">
         <is>
           <t>depend on</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -3799,6 +4209,16 @@
           <t>take care of</t>
         </is>
       </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 照看；处理；清除
@@ -4004,6 +4424,16 @@
           <t>What's wrong?</t>
         </is>
       </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 怎么了；怎么回事；你怎么了</t>
@@ -4014,6 +4444,16 @@
       <c r="A172" s="2" t="inlineStr">
         <is>
           <t>look through</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -4079,6 +4519,16 @@
           <t>big deal</t>
         </is>
       </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">int. 表示不赞同或不以为然
@@ -4093,6 +4543,16 @@
           <t>work out</t>
         </is>
       </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 作出；拟定；制定；计划一下
@@ -4104,6 +4564,16 @@
       <c r="A177" s="2" t="inlineStr">
         <is>
           <t>get on with</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
@@ -4770,6 +5240,16 @@
           <t>compare ... with</t>
         </is>
       </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 和…比较[对照]
@@ -4896,6 +5376,16 @@
           <t>in one's opinion</t>
         </is>
       </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 据某人意见
@@ -4932,6 +5422,16 @@
           <t>Cathy</t>
         </is>
       </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
           <t>n. 凯茜（女子名）</t>
@@ -5011,6 +5511,16 @@
           <t>go off</t>
         </is>
       </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 进行得 (well； badly)；(话等)冒出
@@ -5092,6 +5602,16 @@
           <t>pick up</t>
         </is>
       </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 拾起；探出；重新开始
@@ -5103,6 +5623,16 @@
       <c r="A223" s="2" t="inlineStr">
         <is>
           <t>pick up the phone</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
@@ -5431,6 +5961,16 @@
           <t>fall asleep</t>
         </is>
       </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 入睡
@@ -5442,6 +5982,16 @@
       <c r="A238" s="2" t="inlineStr">
         <is>
           <t>die down</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
@@ -5525,6 +6075,16 @@
       <c r="A242" s="2" t="inlineStr">
         <is>
           <t>have a look</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
@@ -5610,6 +6170,16 @@
           <t>make one's way</t>
         </is>
       </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 前往；发迹
@@ -5737,6 +6307,16 @@
           <t>in silence</t>
         </is>
       </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 沉默着
@@ -5866,6 +6446,16 @@
           <t>at first</t>
         </is>
       </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 首先
@@ -5923,6 +6513,16 @@
           <t>Martin Luther King</t>
         </is>
       </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 马丁·路德·金；金恩博士；马丁路德金恩</t>
@@ -5957,6 +6557,16 @@
           <t>Animal Helpline</t>
         </is>
       </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -5967,6 +6577,16 @@
       <c r="A264" s="2" t="inlineStr">
         <is>
           <t>World Trade Center</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
@@ -6124,6 +6744,16 @@
           <t>a little bit</t>
         </is>
       </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 一点
@@ -6182,6 +6812,16 @@
       <c r="A274" s="2" t="inlineStr">
         <is>
           <t>turn ... into</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
@@ -6365,6 +7005,16 @@
           <t>once upon a time</t>
         </is>
       </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 从前；很久很久以前；古时候
@@ -6421,6 +7071,16 @@
       <c r="A285" s="2" t="inlineStr">
         <is>
           <t>fall in love</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
@@ -7031,6 +7691,16 @@
           <t>Journey to the West</t>
         </is>
       </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 西游记；西行之旅；新版西游记</t>
@@ -7043,6 +7713,16 @@
           <t>the Monkey King</t>
         </is>
       </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 大闹天宫；猴王；美猴王</t>
@@ -7055,6 +7735,16 @@
           <t>Sleeping Beauty</t>
         </is>
       </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 睡了很长时间的人
@@ -7090,6 +7780,16 @@
           <t>Little Red Riding Hood</t>
         </is>
       </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 小红帽；小红帽的故事；小红帽·格林童话</t>
@@ -7100,6 +7800,16 @@
       <c r="A316" s="2" t="inlineStr">
         <is>
           <t>Hansel and Gretel</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
@@ -7282,6 +7992,16 @@
           <t>feel free</t>
         </is>
       </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 感到自由，无拘束; &lt;非正&gt;随自己之意（做某事）</t>
@@ -7463,6 +8183,16 @@
           <t>as far as I know</t>
         </is>
       </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. (= so far as I know)就我所知
@@ -7634,6 +8364,16 @@
           <t>take in</t>
         </is>
       </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 加以考虑；〔美国〕访问；收进；收容
@@ -7693,6 +8433,16 @@
           <t>in the face of</t>
         </is>
       </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 不避；不管；〈英〉在…前面；面临
@@ -7776,6 +8526,16 @@
           <t>even though</t>
         </is>
       </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. “even if”的变体
@@ -7789,6 +8549,16 @@
           <t>even if</t>
         </is>
       </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 即使…也
@@ -7825,6 +8595,16 @@
           <t>the Pacific Ocean</t>
         </is>
       </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 太平洋
@@ -7836,6 +8616,16 @@
       <c r="A351" s="2" t="inlineStr">
         <is>
           <t>cm</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
@@ -7940,6 +8730,16 @@
           <t>at birth</t>
         </is>
       </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 在出生时；刚出生；生下来时</t>
@@ -7950,6 +8750,16 @@
       <c r="A357" s="2" t="inlineStr">
         <is>
           <t>up to</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
@@ -8127,6 +8937,16 @@
           <t>walk into</t>
         </is>
       </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 走进；〈俚〉打骂(仆人等)；〈俚〉大吃
@@ -8140,6 +8960,16 @@
           <t>fall over</t>
         </is>
       </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 倒了；落在地上；(计算机)程序停止运行；跌倒
@@ -8151,6 +8981,16 @@
       <c r="A367" s="2" t="inlineStr">
         <is>
           <t>or so</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
@@ -8329,6 +9169,16 @@
           <t>Tenzing Norgay</t>
         </is>
       </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 诺盖；诺尔盖；丹增诺盖</t>
@@ -8341,6 +9191,16 @@
           <t>Edmund Hillary</t>
         </is>
       </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 希拉里；埃德蒙·希拉里；希拉瑞</t>
@@ -8353,6 +9213,16 @@
           <t>Junko Tabei</t>
         </is>
       </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -8365,6 +9235,16 @@
           <t>Qomolangma</t>
         </is>
       </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 珠穆朗玛峰；西藏珠穆朗玛峰；珠峰</t>
@@ -8377,6 +9257,16 @@
           <t>the Nile</t>
         </is>
       </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 尼罗河；畅游尼罗河；扔入尼罗河</t>
@@ -8389,6 +9279,16 @@
           <t>the Caspian Sea</t>
         </is>
       </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 里海；沿著里海</t>
@@ -8401,6 +9301,16 @@
           <t>the Sahara</t>
         </is>
       </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
           <t>n.撒哈拉</t>
@@ -8413,6 +9323,16 @@
           <t>the Yangtze River</t>
         </is>
       </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 长江
@@ -8426,6 +9346,16 @@
           <t>the Yellow River</t>
         </is>
       </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 黄河；黄河是；河流</t>
@@ -8438,6 +9368,16 @@
           <t>the Ming Dynasty</t>
         </is>
       </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -8450,6 +9390,16 @@
           <t>the Ming Great Wall</t>
         </is>
       </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -8462,6 +9412,16 @@
           <t>the Himalayas</t>
         </is>
       </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 喜马拉雅山；喜马拉雅山脉；喜玛拉雅山脉</t>
@@ -8474,6 +9434,16 @@
           <t>the Amazon River</t>
         </is>
       </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -8484,6 +9454,16 @@
       <c r="A388" s="2" t="inlineStr">
         <is>
           <t>Chengdu Research Base</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
@@ -8545,6 +9525,16 @@
       <c r="A391" s="2" t="inlineStr">
         <is>
           <t>full of</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
@@ -9126,6 +10116,16 @@
           <t>ever since</t>
         </is>
       </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 从…以来
@@ -9253,6 +10253,16 @@
       <c r="A422" s="2" t="inlineStr">
         <is>
           <t>one another</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
@@ -9410,6 +10420,16 @@
           <t>Alex</t>
         </is>
       </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
           <t>n. 亚历克斯（男子名）</t>
@@ -9422,6 +10442,16 @@
           <t>Garth Brooks</t>
         </is>
       </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -9434,6 +10464,16 @@
           <t>The Beatles</t>
         </is>
       </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 披头士乐队；披头四；甲壳虫乐队</t>
@@ -9446,6 +10486,16 @@
           <t>Treasure Island</t>
         </is>
       </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 金银岛；宝岛；珍宝岛</t>
@@ -9458,6 +10508,16 @@
           <t>Alice in Wonderland</t>
         </is>
       </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. （事情悖理且与想象的截然相反的）怪异局面
@@ -9471,6 +10531,16 @@
           <t>Little Women</t>
         </is>
       </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
           <t>小妇人（美国作家露依莎·奥尔柯特的作品）</t>
@@ -9483,6 +10553,16 @@
           <t>Oliver Twist</t>
         </is>
       </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 雾都孤儿；苦海孤雏；孤雏泪</t>
@@ -9495,6 +10575,16 @@
           <t>Robinson Crusoe</t>
         </is>
       </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 鲁宾逊
@@ -9508,6 +10598,16 @@
           <t>Tom Sawyer</t>
         </is>
       </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 汤姆历险记；汤姆·索亚；汤姆·索亚历险记</t>
@@ -9520,6 +10620,16 @@
           <t>Harry Potter</t>
         </is>
       </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
           <t>哈利·波特（著名系列小说《哈利·波特》中的主人公）</t>
@@ -9576,6 +10686,16 @@
           <t>Country Music Hall of Fame Museum</t>
         </is>
       </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -9608,6 +10728,16 @@
       <c r="A443" s="2" t="inlineStr">
         <is>
           <t>amusement park</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D443" s="2" t="inlineStr">
@@ -9893,6 +11023,16 @@
       <c r="A456" s="2" t="inlineStr">
         <is>
           <t>tea art</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
@@ -10026,6 +11166,16 @@
           <t>a couple of</t>
         </is>
       </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">det. 一对
@@ -10155,6 +11305,16 @@
           <t>thousands of</t>
         </is>
       </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">adj. 几千；成千上万
@@ -10166,6 +11326,16 @@
       <c r="A469" s="2" t="inlineStr">
         <is>
           <t>on the one hand ... on the other hand ...</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D469" s="2" t="inlineStr">
@@ -10342,6 +11512,16 @@
       <c r="A477" s="2" t="inlineStr">
         <is>
           <t>all year round</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D477" s="2" t="inlineStr">
@@ -10471,6 +11651,16 @@
           <t>National Science Museum</t>
         </is>
       </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 国家科学博物馆；国家自然博物馆；国立科学博物馆</t>
@@ -10483,6 +11673,16 @@
           <t>International Museum of Toilets</t>
         </is>
       </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -10495,6 +11695,16 @@
           <t>Hangzhou National Tea Museum</t>
         </is>
       </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -10507,6 +11717,16 @@
           <t>Donald Duck</t>
         </is>
       </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 唐老鸭；唐老鸦；唐老鸭与黛丝姑娘</t>
@@ -10541,6 +11761,16 @@
           <t>Disney Cruise</t>
         </is>
       </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -10553,6 +11783,16 @@
           <t>the Terracotta Army</t>
         </is>
       </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -10565,6 +11805,16 @@
           <t>the Bird's Nest</t>
         </is>
       </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -10599,6 +11849,16 @@
           <t>Southeast Asia</t>
         </is>
       </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 东南亚
@@ -10612,6 +11872,16 @@
           <t>Night Safari</t>
         </is>
       </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -10646,6 +11916,16 @@
       <c r="A495" s="2" t="inlineStr">
         <is>
           <t>yard sale</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D495" s="2" t="inlineStr">
@@ -10805,6 +12085,16 @@
           <t>bread maker</t>
         </is>
       </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 面包机；制面包机；面包机特价</t>
@@ -10864,6 +12154,16 @@
           <t>soft toy</t>
         </is>
       </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. （动物造型的）软体玩具
@@ -10950,6 +12250,16 @@
           <t>board game</t>
         </is>
       </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 【游】桌上游戏
@@ -10985,6 +12295,16 @@
       <c r="A511" s="2" t="inlineStr">
         <is>
           <t>junior high school</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D511" s="2" t="inlineStr">
@@ -11027,6 +12347,16 @@
           <t>clear out</t>
         </is>
       </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 清空；腾空；清理；〈非正式〉匆忙离开
@@ -11061,6 +12391,16 @@
       <c r="A515" s="2" t="inlineStr">
         <is>
           <t>no longer</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D515" s="2" t="inlineStr">
@@ -11152,6 +12492,16 @@
           <t>part with</t>
         </is>
       </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 跟…分别；解雇；卖掉(东西)
@@ -11189,6 +12539,16 @@
           <t>as for</t>
         </is>
       </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D521" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 至于
@@ -11222,6 +12582,16 @@
       <c r="A523" s="2" t="inlineStr">
         <is>
           <t>to be honest</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D523" s="2" t="inlineStr">
@@ -11491,6 +12861,16 @@
       <c r="A535" s="2" t="inlineStr">
         <is>
           <t>according to</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D535" s="2" t="inlineStr">
@@ -11596,6 +12976,16 @@
       <c r="A540" s="2" t="inlineStr">
         <is>
           <t>close to</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D540" s="2" t="inlineStr">
